--- a/public/templates/MRF_template.xlsx
+++ b/public/templates/MRF_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{23099513-DBF9-4958-ABB1-A9A40AFD9BA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2C47FFA8-27DE-4A98-95B3-AAD8BF66E069}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D0198B82-F0F5-48E3-BCED-1601A3552D56}"/>
   </bookViews>
@@ -857,6 +857,69 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -882,69 +945,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -1449,7 +1449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B700CE7C-2478-4AAA-891F-66C41E0F6824}">
-  <dimension ref="A1:L57"/>
+  <dimension ref="A1:L66"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.5703125" style="1" customWidth="1"/>
@@ -1467,15 +1467,15 @@
       <c r="E1" s="16"/>
     </row>
     <row r="2" spans="1:12" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A2" s="80" t="s">
+      <c r="A2" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="80"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
+      <c r="B2" s="96"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="96"/>
+      <c r="E2" s="96"/>
+      <c r="F2" s="96"/>
+      <c r="G2" s="96"/>
     </row>
     <row r="3" spans="1:12" ht="26.25" x14ac:dyDescent="0.4">
       <c r="C3" s="34"/>
@@ -1505,9 +1505,9 @@
       <c r="D6" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="81"/>
-      <c r="F6" s="81"/>
-      <c r="G6" s="81"/>
+      <c r="E6" s="97"/>
+      <c r="F6" s="97"/>
+      <c r="G6" s="97"/>
     </row>
     <row r="7" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A7" s="6"/>
@@ -1527,9 +1527,9 @@
       <c r="D8" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="87"/>
-      <c r="F8" s="87"/>
-      <c r="G8" s="87"/>
+      <c r="E8" s="103"/>
+      <c r="F8" s="103"/>
+      <c r="G8" s="103"/>
     </row>
     <row r="9" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A9" s="13"/>
@@ -1549,9 +1549,9 @@
       <c r="D10" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="87"/>
-      <c r="F10" s="87"/>
-      <c r="G10" s="87"/>
+      <c r="E10" s="103"/>
+      <c r="F10" s="103"/>
+      <c r="G10" s="103"/>
       <c r="H10" s="19"/>
       <c r="I10" s="19"/>
       <c r="J10" s="19"/>
@@ -1563,9 +1563,9 @@
       <c r="B11" s="16"/>
       <c r="C11" s="17"/>
       <c r="D11" s="10"/>
-      <c r="E11" s="82"/>
-      <c r="F11" s="82"/>
-      <c r="G11" s="82"/>
+      <c r="E11" s="98"/>
+      <c r="F11" s="98"/>
+      <c r="G11" s="98"/>
       <c r="H11" s="19"/>
       <c r="I11" s="19"/>
       <c r="J11" s="19"/>
@@ -1581,9 +1581,9 @@
       <c r="D12" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="83"/>
-      <c r="F12" s="83"/>
-      <c r="G12" s="83"/>
+      <c r="E12" s="99"/>
+      <c r="F12" s="99"/>
+      <c r="G12" s="99"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
@@ -1605,23 +1605,23 @@
       <c r="L13" s="19"/>
     </row>
     <row r="14" spans="1:12" s="24" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="84" t="s">
+      <c r="A14" s="100" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="85" t="s">
+      <c r="B14" s="101" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="85" t="s">
+      <c r="C14" s="101" t="s">
         <v>11</v>
       </c>
-      <c r="D14" s="85" t="s">
+      <c r="D14" s="101" t="s">
         <v>12</v>
       </c>
-      <c r="E14" s="86"/>
-      <c r="F14" s="85" t="s">
+      <c r="E14" s="102"/>
+      <c r="F14" s="101" t="s">
         <v>13</v>
       </c>
-      <c r="G14" s="85"/>
+      <c r="G14" s="101"/>
       <c r="H14" s="23"/>
       <c r="I14" s="23"/>
       <c r="J14" s="23"/>
@@ -1629,13 +1629,13 @@
       <c r="L14" s="23"/>
     </row>
     <row r="15" spans="1:12" s="24" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="84"/>
-      <c r="B15" s="85"/>
-      <c r="C15" s="86"/>
-      <c r="D15" s="86"/>
-      <c r="E15" s="86"/>
-      <c r="F15" s="85"/>
-      <c r="G15" s="85"/>
+      <c r="A15" s="100"/>
+      <c r="B15" s="101"/>
+      <c r="C15" s="102"/>
+      <c r="D15" s="102"/>
+      <c r="E15" s="102"/>
+      <c r="F15" s="101"/>
+      <c r="G15" s="101"/>
       <c r="H15" s="23"/>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
@@ -1643,17 +1643,17 @@
       <c r="L15" s="23"/>
     </row>
     <row r="16" spans="1:12" s="24" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A16" s="84"/>
-      <c r="B16" s="85"/>
-      <c r="C16" s="86"/>
-      <c r="D16" s="85" t="s">
+      <c r="A16" s="100"/>
+      <c r="B16" s="101"/>
+      <c r="C16" s="102"/>
+      <c r="D16" s="101" t="s">
         <v>14</v>
       </c>
-      <c r="E16" s="85"/>
-      <c r="F16" s="85" t="s">
+      <c r="E16" s="101"/>
+      <c r="F16" s="101" t="s">
         <v>14</v>
       </c>
-      <c r="G16" s="86"/>
+      <c r="G16" s="102"/>
       <c r="H16" s="23"/>
       <c r="I16" s="23"/>
       <c r="J16" s="23"/>
@@ -1661,9 +1661,9 @@
       <c r="L16" s="23"/>
     </row>
     <row r="17" spans="1:12" s="24" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="84"/>
-      <c r="B17" s="85"/>
-      <c r="C17" s="86"/>
+      <c r="A17" s="100"/>
+      <c r="B17" s="101"/>
+      <c r="C17" s="102"/>
       <c r="D17" s="33" t="s">
         <v>15</v>
       </c>
@@ -1781,7 +1781,7 @@
       <c r="L24" s="23"/>
     </row>
     <row r="25" spans="1:12" s="24" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="54"/>
+      <c r="A25" s="53"/>
       <c r="B25" s="35"/>
       <c r="C25" s="38"/>
       <c r="D25" s="39"/>
@@ -1794,121 +1794,133 @@
       <c r="K25" s="23"/>
       <c r="L25" s="23"/>
     </row>
-    <row r="26" spans="1:12" s="24" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="91" t="s">
-        <v>29</v>
-      </c>
-      <c r="B26" s="91"/>
-      <c r="C26" s="91"/>
-      <c r="D26" s="91"/>
-      <c r="E26" s="91"/>
-      <c r="F26" s="91"/>
-      <c r="G26" s="91"/>
-      <c r="H26" s="23"/>
+    <row r="26" spans="1:12" s="24" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="53"/>
+      <c r="B26" s="35"/>
+      <c r="C26" s="38"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="57"/>
+      <c r="F26" s="59"/>
+      <c r="G26" s="59"/>
+      <c r="H26" s="69"/>
       <c r="I26" s="23"/>
       <c r="J26" s="23"/>
       <c r="K26" s="23"/>
       <c r="L26" s="23"/>
     </row>
-    <row r="27" spans="1:12" s="24" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="35"/>
+    <row r="27" spans="1:12" s="24" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="53"/>
       <c r="B27" s="35"/>
-      <c r="C27" s="41"/>
-      <c r="D27" s="45"/>
-      <c r="E27" s="42"/>
-      <c r="F27" s="25"/>
-      <c r="G27" s="25"/>
-      <c r="H27" s="70"/>
-    </row>
-    <row r="28" spans="1:12" s="24" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="55"/>
-      <c r="B28" s="43"/>
-      <c r="C28" s="44"/>
-      <c r="D28" s="45"/>
-      <c r="E28" s="42"/>
-      <c r="F28" s="26"/>
-      <c r="G28" s="26"/>
-      <c r="H28" s="72"/>
-    </row>
-    <row r="29" spans="1:12" s="24" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="58"/>
-      <c r="B29" s="36"/>
-      <c r="C29" s="44"/>
-      <c r="D29" s="45"/>
-      <c r="E29" s="42"/>
-      <c r="F29" s="26"/>
-      <c r="G29" s="26"/>
-      <c r="H29" s="72"/>
+      <c r="C27" s="38"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="57"/>
+      <c r="F27" s="59"/>
+      <c r="G27" s="59"/>
+      <c r="H27" s="69"/>
+      <c r="I27" s="23"/>
+      <c r="J27" s="23"/>
+      <c r="K27" s="23"/>
+      <c r="L27" s="23"/>
+    </row>
+    <row r="28" spans="1:12" s="24" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="54"/>
+      <c r="B28" s="35"/>
+      <c r="C28" s="38"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="57"/>
+      <c r="F28" s="59"/>
+      <c r="G28" s="59"/>
+      <c r="H28" s="69"/>
+      <c r="I28" s="23"/>
+      <c r="J28" s="23"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="23"/>
+    </row>
+    <row r="29" spans="1:12" s="24" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="83" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" s="83"/>
+      <c r="C29" s="83"/>
+      <c r="D29" s="83"/>
+      <c r="E29" s="83"/>
+      <c r="F29" s="83"/>
+      <c r="G29" s="83"/>
+      <c r="H29" s="23"/>
+      <c r="I29" s="23"/>
+      <c r="J29" s="23"/>
+      <c r="K29" s="23"/>
+      <c r="L29" s="23"/>
     </row>
     <row r="30" spans="1:12" s="24" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="55"/>
-      <c r="B30" s="43"/>
-      <c r="C30" s="46"/>
+      <c r="A30" s="35"/>
+      <c r="B30" s="35"/>
+      <c r="C30" s="41"/>
       <c r="D30" s="45"/>
       <c r="E30" s="42"/>
-      <c r="F30" s="26"/>
-      <c r="G30" s="26"/>
-      <c r="H30" s="72"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="25"/>
+      <c r="H30" s="70"/>
     </row>
     <row r="31" spans="1:12" s="24" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="55"/>
       <c r="B31" s="43"/>
-      <c r="C31" s="46"/>
+      <c r="C31" s="44"/>
       <c r="D31" s="45"/>
       <c r="E31" s="42"/>
-      <c r="F31" s="47"/>
+      <c r="F31" s="26"/>
       <c r="G31" s="26"/>
       <c r="H31" s="72"/>
     </row>
     <row r="32" spans="1:12" s="24" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="55"/>
-      <c r="B32" s="43"/>
-      <c r="C32" s="46"/>
+      <c r="A32" s="58"/>
+      <c r="B32" s="36"/>
+      <c r="C32" s="44"/>
       <c r="D32" s="45"/>
       <c r="E32" s="42"/>
-      <c r="F32" s="47"/>
+      <c r="F32" s="26"/>
       <c r="G32" s="26"/>
       <c r="H32" s="72"/>
     </row>
     <row r="33" spans="1:8" s="24" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="55"/>
       <c r="B33" s="43"/>
-      <c r="C33" s="27"/>
-      <c r="D33" s="48"/>
+      <c r="C33" s="46"/>
+      <c r="D33" s="45"/>
       <c r="E33" s="42"/>
-      <c r="F33" s="25"/>
-      <c r="G33" s="25"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
       <c r="H33" s="72"/>
     </row>
-    <row r="34" spans="1:8" s="24" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8" s="24" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="55"/>
       <c r="B34" s="43"/>
-      <c r="C34" s="27"/>
-      <c r="D34" s="36"/>
-      <c r="E34" s="49"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="23"/>
-    </row>
-    <row r="35" spans="1:8" s="24" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C34" s="46"/>
+      <c r="D34" s="45"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="47"/>
+      <c r="G34" s="26"/>
+      <c r="H34" s="72"/>
+    </row>
+    <row r="35" spans="1:8" s="24" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="55"/>
       <c r="B35" s="43"/>
-      <c r="C35" s="27"/>
-      <c r="D35" s="36"/>
-      <c r="E35" s="49"/>
-      <c r="F35" s="25"/>
-      <c r="G35" s="25"/>
-      <c r="H35" s="23"/>
-    </row>
-    <row r="36" spans="1:8" s="24" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C35" s="46"/>
+      <c r="D35" s="45"/>
+      <c r="E35" s="42"/>
+      <c r="F35" s="47"/>
+      <c r="G35" s="26"/>
+      <c r="H35" s="72"/>
+    </row>
+    <row r="36" spans="1:8" s="24" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="55"/>
       <c r="B36" s="43"/>
       <c r="C36" s="27"/>
-      <c r="D36" s="36"/>
-      <c r="E36" s="49"/>
+      <c r="D36" s="48"/>
+      <c r="E36" s="42"/>
       <c r="F36" s="25"/>
       <c r="G36" s="25"/>
-      <c r="H36" s="23"/>
+      <c r="H36" s="72"/>
     </row>
     <row r="37" spans="1:8" s="24" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="55"/>
@@ -1920,192 +1932,266 @@
       <c r="G37" s="25"/>
       <c r="H37" s="23"/>
     </row>
-    <row r="38" spans="1:8" s="24" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="56"/>
-      <c r="B38" s="50"/>
-      <c r="C38" s="44"/>
+    <row r="38" spans="1:8" s="24" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="55"/>
+      <c r="B38" s="43"/>
+      <c r="C38" s="27"/>
       <c r="D38" s="36"/>
-      <c r="E38" s="42"/>
-      <c r="F38" s="61"/>
+      <c r="E38" s="49"/>
+      <c r="F38" s="25"/>
       <c r="G38" s="25"/>
-      <c r="H38" s="73"/>
-    </row>
-    <row r="39" spans="1:8" s="24" customFormat="1" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="35"/>
-      <c r="B39" s="35"/>
-      <c r="C39" s="44"/>
-      <c r="D39" s="51"/>
-      <c r="E39" s="42"/>
-      <c r="F39" s="61"/>
+      <c r="H38" s="23"/>
+    </row>
+    <row r="39" spans="1:8" s="24" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="55"/>
+      <c r="B39" s="43"/>
+      <c r="C39" s="27"/>
+      <c r="D39" s="36"/>
+      <c r="E39" s="49"/>
+      <c r="F39" s="25"/>
       <c r="G39" s="25"/>
-      <c r="H39" s="73"/>
-    </row>
-    <row r="40" spans="1:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="35"/>
-      <c r="B40" s="35"/>
+      <c r="H39" s="23"/>
+    </row>
+    <row r="40" spans="1:8" s="24" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="55"/>
+      <c r="B40" s="43"/>
       <c r="C40" s="27"/>
-      <c r="D40" s="48"/>
-      <c r="E40" s="42"/>
-      <c r="F40" s="30"/>
-      <c r="G40" s="30"/>
-      <c r="H40" s="19"/>
-    </row>
-    <row r="41" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="35"/>
-      <c r="B41" s="35"/>
-      <c r="C41" s="52"/>
-      <c r="D41" s="66"/>
+      <c r="D40" s="36"/>
+      <c r="E40" s="49"/>
+      <c r="F40" s="25"/>
+      <c r="G40" s="25"/>
+      <c r="H40" s="23"/>
+    </row>
+    <row r="41" spans="1:8" s="24" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="56"/>
+      <c r="B41" s="50"/>
+      <c r="C41" s="44"/>
+      <c r="D41" s="36"/>
       <c r="E41" s="42"/>
-      <c r="F41" s="62"/>
-      <c r="G41" s="30"/>
-      <c r="H41" s="74"/>
-    </row>
-    <row r="42" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F41" s="61"/>
+      <c r="G41" s="25"/>
+      <c r="H41" s="73"/>
+    </row>
+    <row r="42" spans="1:8" s="24" customFormat="1" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="35"/>
       <c r="B42" s="35"/>
-      <c r="C42" s="52"/>
-      <c r="D42" s="66"/>
+      <c r="C42" s="44"/>
+      <c r="D42" s="51"/>
       <c r="E42" s="42"/>
-      <c r="F42" s="30"/>
-      <c r="G42" s="30"/>
-    </row>
-    <row r="43" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F42" s="61"/>
+      <c r="G42" s="25"/>
+      <c r="H42" s="73"/>
+    </row>
+    <row r="43" spans="1:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="35"/>
       <c r="B43" s="35"/>
-      <c r="C43" s="52"/>
-      <c r="D43" s="67"/>
+      <c r="C43" s="27"/>
+      <c r="D43" s="48"/>
       <c r="E43" s="42"/>
       <c r="F43" s="30"/>
       <c r="G43" s="30"/>
-    </row>
-    <row r="44" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H43" s="19"/>
+    </row>
+    <row r="44" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="35"/>
       <c r="B44" s="35"/>
       <c r="C44" s="52"/>
-      <c r="D44" s="67"/>
+      <c r="D44" s="66"/>
       <c r="E44" s="42"/>
-      <c r="F44" s="30"/>
+      <c r="F44" s="62"/>
       <c r="G44" s="30"/>
-    </row>
-    <row r="45" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="78"/>
-      <c r="B45" s="78"/>
+      <c r="H44" s="74"/>
+    </row>
+    <row r="45" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="35"/>
+      <c r="B45" s="35"/>
       <c r="C45" s="52"/>
-      <c r="D45" s="79"/>
+      <c r="D45" s="66"/>
       <c r="E45" s="42"/>
       <c r="F45" s="30"/>
       <c r="G45" s="30"/>
     </row>
-    <row r="46" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="35"/>
       <c r="B46" s="35"/>
-      <c r="C46" s="38"/>
-      <c r="D46" s="37"/>
+      <c r="C46" s="52"/>
+      <c r="D46" s="67"/>
       <c r="E46" s="42"/>
       <c r="F46" s="30"/>
       <c r="G46" s="30"/>
     </row>
-    <row r="47" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="29" t="s">
+    <row r="47" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="35"/>
+      <c r="B47" s="35"/>
+      <c r="C47" s="52"/>
+      <c r="D47" s="67"/>
+      <c r="E47" s="42"/>
+      <c r="F47" s="30"/>
+      <c r="G47" s="30"/>
+    </row>
+    <row r="48" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="35"/>
+      <c r="B48" s="35"/>
+      <c r="C48" s="52"/>
+      <c r="D48" s="67"/>
+      <c r="E48" s="42"/>
+      <c r="F48" s="30"/>
+      <c r="G48" s="30"/>
+    </row>
+    <row r="49" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="35"/>
+      <c r="B49" s="35"/>
+      <c r="C49" s="52"/>
+      <c r="D49" s="67"/>
+      <c r="E49" s="42"/>
+      <c r="F49" s="30"/>
+      <c r="G49" s="30"/>
+    </row>
+    <row r="50" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="35"/>
+      <c r="B50" s="35"/>
+      <c r="C50" s="52"/>
+      <c r="D50" s="67"/>
+      <c r="E50" s="42"/>
+      <c r="F50" s="30"/>
+      <c r="G50" s="30"/>
+    </row>
+    <row r="51" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="35"/>
+      <c r="B51" s="35"/>
+      <c r="C51" s="52"/>
+      <c r="D51" s="67"/>
+      <c r="E51" s="42"/>
+      <c r="F51" s="30"/>
+      <c r="G51" s="30"/>
+    </row>
+    <row r="52" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="35"/>
+      <c r="B52" s="35"/>
+      <c r="C52" s="52"/>
+      <c r="D52" s="67"/>
+      <c r="E52" s="42"/>
+      <c r="F52" s="30"/>
+      <c r="G52" s="30"/>
+    </row>
+    <row r="53" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="35"/>
+      <c r="B53" s="35"/>
+      <c r="C53" s="52"/>
+      <c r="D53" s="67"/>
+      <c r="E53" s="42"/>
+      <c r="F53" s="30"/>
+      <c r="G53" s="30"/>
+    </row>
+    <row r="54" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="78"/>
+      <c r="B54" s="78"/>
+      <c r="C54" s="52"/>
+      <c r="D54" s="79"/>
+      <c r="E54" s="42"/>
+      <c r="F54" s="30"/>
+      <c r="G54" s="30"/>
+    </row>
+    <row r="55" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="35"/>
+      <c r="B55" s="35"/>
+      <c r="C55" s="38"/>
+      <c r="D55" s="37"/>
+      <c r="E55" s="42"/>
+      <c r="F55" s="30"/>
+      <c r="G55" s="30"/>
+    </row>
+    <row r="56" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="B47" s="89" t="s">
+      <c r="B56" s="81" t="s">
         <v>31</v>
       </c>
-      <c r="C47" s="94" t="s">
+      <c r="C56" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="D47" s="100"/>
-      <c r="E47" s="100"/>
-      <c r="F47" s="100"/>
-      <c r="G47" s="101"/>
-    </row>
-    <row r="48" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="92" t="s">
+      <c r="D56" s="92"/>
+      <c r="E56" s="92"/>
+      <c r="F56" s="92"/>
+      <c r="G56" s="93"/>
+    </row>
+    <row r="57" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="84" t="s">
         <v>32</v>
       </c>
-      <c r="B48" s="90"/>
-      <c r="C48" s="95"/>
-      <c r="D48" s="102"/>
-      <c r="E48" s="102"/>
-      <c r="F48" s="102"/>
-      <c r="G48" s="103"/>
-    </row>
-    <row r="49" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="93"/>
-      <c r="B49" s="89" t="s">
+      <c r="B57" s="82"/>
+      <c r="C57" s="87"/>
+      <c r="D57" s="94"/>
+      <c r="E57" s="94"/>
+      <c r="F57" s="94"/>
+      <c r="G57" s="95"/>
+    </row>
+    <row r="58" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="85"/>
+      <c r="B58" s="81" t="s">
         <v>19</v>
       </c>
-      <c r="C49" s="94" t="s">
+      <c r="C58" s="86" t="s">
         <v>26</v>
       </c>
-      <c r="D49" s="96"/>
-      <c r="E49" s="96"/>
-      <c r="F49" s="96"/>
-      <c r="G49" s="97"/>
-    </row>
-    <row r="50" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="30" t="s">
+      <c r="D58" s="88"/>
+      <c r="E58" s="88"/>
+      <c r="F58" s="88"/>
+      <c r="G58" s="89"/>
+    </row>
+    <row r="59" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="B50" s="90"/>
-      <c r="C50" s="95"/>
-      <c r="D50" s="98"/>
-      <c r="E50" s="98"/>
-      <c r="F50" s="98"/>
-      <c r="G50" s="99"/>
-    </row>
-    <row r="51" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B51" s="30" t="s">
+      <c r="B59" s="82"/>
+      <c r="C59" s="87"/>
+      <c r="D59" s="90"/>
+      <c r="E59" s="90"/>
+      <c r="F59" s="90"/>
+      <c r="G59" s="91"/>
+    </row>
+    <row r="60" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B60" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="C51" s="65" t="s">
+      <c r="C60" s="65" t="s">
         <v>27</v>
       </c>
-      <c r="D51" s="63"/>
-      <c r="E51" s="68"/>
-      <c r="F51" s="63"/>
-      <c r="G51" s="64"/>
-    </row>
-    <row r="53" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C54" s="1" t="s">
+      <c r="D60" s="63"/>
+      <c r="E60" s="68"/>
+      <c r="F60" s="63"/>
+      <c r="G60" s="64"/>
+    </row>
+    <row r="62" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C63" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D54" s="31"/>
-    </row>
-    <row r="55" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C55" s="1" t="s">
+      <c r="D63" s="31"/>
+    </row>
+    <row r="64" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C64" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C56" s="1" t="s">
+    <row r="65" spans="3:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C65" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D56" s="31"/>
-      <c r="E56" s="32" t="s">
+      <c r="D65" s="31"/>
+      <c r="E65" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="F56" s="75"/>
-      <c r="G56" s="28"/>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="F57" s="88"/>
-      <c r="G57" s="88"/>
+      <c r="F65" s="75"/>
+      <c r="G65" s="28"/>
+    </row>
+    <row r="66" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="F66" s="80"/>
+      <c r="G66" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="F57:G57"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="D49:G50"/>
-    <mergeCell ref="D47:G47"/>
-    <mergeCell ref="D48:G48"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="E6:G6"/>
     <mergeCell ref="E11:G12"/>
@@ -2118,6 +2204,16 @@
     <mergeCell ref="E8:G8"/>
     <mergeCell ref="E10:G10"/>
     <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A57:A58"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:G59"/>
+    <mergeCell ref="D56:G56"/>
+    <mergeCell ref="D57:G57"/>
   </mergeCells>
   <phoneticPr fontId="29" type="noConversion"/>
   <conditionalFormatting sqref="A18">
@@ -2138,28 +2234,28 @@
   <conditionalFormatting sqref="A23">
     <cfRule type="duplicateValues" dxfId="8" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A24">
+  <conditionalFormatting sqref="A24:A27">
     <cfRule type="duplicateValues" dxfId="7" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A25:A26">
+  <conditionalFormatting sqref="A28:A29">
     <cfRule type="duplicateValues" dxfId="6" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A27">
+  <conditionalFormatting sqref="A30">
     <cfRule type="duplicateValues" dxfId="5" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A29">
+  <conditionalFormatting sqref="A32">
     <cfRule type="duplicateValues" dxfId="4" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A39">
+  <conditionalFormatting sqref="A42">
     <cfRule type="duplicateValues" dxfId="3" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A41">
+  <conditionalFormatting sqref="A44">
     <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A42:A44">
+  <conditionalFormatting sqref="A45:A53">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A46">
+  <conditionalFormatting sqref="A55">
     <cfRule type="duplicateValues" dxfId="0" priority="15"/>
   </conditionalFormatting>
   <pageMargins left="0.23599999999999999" right="0.23599999999999999" top="0.35399999999999998" bottom="0.748" header="0.3" footer="0.3"/>
@@ -2169,18 +2265,29 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="34c87397-5fc1-491e-85e7-d6110dbe9cbd" ContentTypeId="0x010100CE50E52E7543470BBDD3827FE50C59CB" PreviousValue="false"/>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Owner xmlns="71c5aaf6-e6ce-465b-b873-5148d2a4c105" xsi:nil="true"/>
+    <DocumentType xmlns="71c5aaf6-e6ce-465b-b873-5148d2a4c105">Description</DocumentType>
+    <NokiaConfidentiality xmlns="71c5aaf6-e6ce-465b-b873-5148d2a4c105">Nokia Internal Use</NokiaConfidentiality>
+    <HideFromDelve xmlns="71c5aaf6-e6ce-465b-b873-5148d2a4c105">false</HideFromDelve>
+    <EXECUTE_x0020_Content xmlns="31aacdf4-fb95-42ec-80aa-6fc76e563ffe" xsi:nil="true"/>
+    <_dlc_DocId xmlns="71c5aaf6-e6ce-465b-b873-5148d2a4c105">4NIMP5LIAM4P-487227298-104996</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="71c5aaf6-e6ce-465b-b873-5148d2a4c105">
+      <Url>https://nokia.sharepoint.com/sites/FN_EXECUTE_Projects_01/19.PH.891566/_layouts/15/DocIdRedir.aspx?ID=4NIMP5LIAM4P-487227298-104996</Url>
+      <Description>4NIMP5LIAM4P-487227298-104996</Description>
+    </_dlc_DocIdUrl>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
-<customXsn xmlns="http://schemas.microsoft.com/office/2006/metadata/customXsn">
-  <xsnLocation/>
-  <cached>True</cached>
-  <openByDefault>True</openByDefault>
-  <xsnScope/>
-</customXsn>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2235,28 +2342,17 @@
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<customXsn xmlns="http://schemas.microsoft.com/office/2006/metadata/customXsn">
+  <xsnLocation/>
+  <cached>True</cached>
+  <openByDefault>True</openByDefault>
+  <xsnScope/>
+</customXsn>
 </file>
 
 <file path=customXml/item5.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Owner xmlns="71c5aaf6-e6ce-465b-b873-5148d2a4c105" xsi:nil="true"/>
-    <DocumentType xmlns="71c5aaf6-e6ce-465b-b873-5148d2a4c105">Description</DocumentType>
-    <NokiaConfidentiality xmlns="71c5aaf6-e6ce-465b-b873-5148d2a4c105">Nokia Internal Use</NokiaConfidentiality>
-    <HideFromDelve xmlns="71c5aaf6-e6ce-465b-b873-5148d2a4c105">false</HideFromDelve>
-    <EXECUTE_x0020_Content xmlns="31aacdf4-fb95-42ec-80aa-6fc76e563ffe" xsi:nil="true"/>
-    <_dlc_DocId xmlns="71c5aaf6-e6ce-465b-b873-5148d2a4c105">4NIMP5LIAM4P-487227298-104996</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="71c5aaf6-e6ce-465b-b873-5148d2a4c105">
-      <Url>https://nokia.sharepoint.com/sites/FN_EXECUTE_Projects_01/19.PH.891566/_layouts/15/DocIdRedir.aspx?ID=4NIMP5LIAM4P-487227298-104996</Url>
-      <Description>4NIMP5LIAM4P-487227298-104996</Description>
-    </_dlc_DocIdUrl>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="34c87397-5fc1-491e-85e7-d6110dbe9cbd" ContentTypeId="0x010100CE50E52E7543470BBDD3827FE50C59CB" PreviousValue="false"/>
 </file>
 
 <file path=customXml/item6.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2476,17 +2572,26 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A291274A-4EA0-4E57-B629-E0B27FF3F3C9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4695F569-C332-4377-B336-958B36C084BD}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="71c5aaf6-e6ce-465b-b873-5148d2a4c105"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="31aacdf4-fb95-42ec-80aa-6fc76e563ffe"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14AD1854-13FE-49B8-B5B1-8426C20F7669}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6B4300D-9EFA-4008-840F-6108E8E828B4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/customXsn"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2500,26 +2605,17 @@
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6B4300D-9EFA-4008-840F-6108E8E828B4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14AD1854-13FE-49B8-B5B1-8426C20F7669}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/customXsn"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps5.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4695F569-C332-4377-B336-958B36C084BD}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A291274A-4EA0-4E57-B629-E0B27FF3F3C9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="71c5aaf6-e6ce-465b-b873-5148d2a4c105"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="31aacdf4-fb95-42ec-80aa-6fc76e563ffe"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
